--- a/result/morris/morris_first_inf_ONLY_MAE_N512_seed42.xlsx
+++ b/result/morris/morris_first_inf_ONLY_MAE_N512_seed42.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,65 +453,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.03933376736112</v>
+        <v>-5.967719184027784</v>
       </c>
       <c r="C2" t="n">
-        <v>17.30636935763889</v>
+        <v>17.90955946180556</v>
       </c>
       <c r="D2" t="n">
-        <v>29.1836467411415</v>
+        <v>28.34359024853912</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.17209201388889</v>
+        <v>1.641276041666666</v>
       </c>
       <c r="C3" t="n">
-        <v>17.29177517361113</v>
+        <v>15.1904296875</v>
       </c>
       <c r="D3" t="n">
-        <v>23.9383425369756</v>
+        <v>26.16499393519895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-9.678493923611121</v>
+        <v>1.169921875</v>
       </c>
       <c r="C4" t="n">
-        <v>16.23741319444444</v>
+        <v>13.85405815972222</v>
       </c>
       <c r="D4" t="n">
-        <v>27.96135002087676</v>
+        <v>22.07605669343739</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.80767144097222</v>
+        <v>4.826117621527776</v>
       </c>
       <c r="C5" t="n">
-        <v>15.13481987847222</v>
+        <v>12.76166449652777</v>
       </c>
       <c r="D5" t="n">
-        <v>19.74882228841502</v>
+        <v>21.67651698924342</v>
       </c>
     </row>
     <row r="6">
@@ -521,29 +521,29 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2328016493055557</v>
+        <v>0.5689561631944445</v>
       </c>
       <c r="C6" t="n">
-        <v>6.679633246527779</v>
+        <v>8.879069010416677</v>
       </c>
       <c r="D6" t="n">
-        <v>16.65925184468825</v>
+        <v>17.23667415094495</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.6904296875</v>
+        <v>0.8589952256944443</v>
       </c>
       <c r="C7" t="n">
-        <v>3.200195312500001</v>
+        <v>7.558430989583331</v>
       </c>
       <c r="D7" t="n">
-        <v>8.270962989166462</v>
+        <v>12.94460682415535</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.200792100694446</v>
+        <v>0.2780490451388888</v>
       </c>
       <c r="C8" t="n">
-        <v>2.584906684027778</v>
+        <v>4.634711371527779</v>
       </c>
       <c r="D8" t="n">
-        <v>11.35584546266198</v>
+        <v>13.837427763286</v>
       </c>
     </row>
     <row r="9">
@@ -569,29 +569,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8069118923611113</v>
+        <v>2.560004340277778</v>
       </c>
       <c r="C9" t="n">
-        <v>2.138943142361112</v>
+        <v>4.314778645833336</v>
       </c>
       <c r="D9" t="n">
-        <v>6.871808406238719</v>
+        <v>13.03423766402118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.383734809027778</v>
+        <v>1.359700520833333</v>
       </c>
       <c r="C10" t="n">
-        <v>1.948404947916667</v>
+        <v>3.196072048611115</v>
       </c>
       <c r="D10" t="n">
-        <v>7.524462149702158</v>
+        <v>17.00328456309751</v>
       </c>
     </row>
     <row r="11">
@@ -601,45 +601,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3002387152777779</v>
+        <v>-0.756618923611111</v>
       </c>
       <c r="C11" t="n">
-        <v>1.748806423611111</v>
+        <v>2.917968750000001</v>
       </c>
       <c r="D11" t="n">
-        <v>9.956918023961132</v>
+        <v>9.948626139661901</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5530598958333335</v>
+        <v>0.7405056423611114</v>
       </c>
       <c r="C12" t="n">
-        <v>1.34299045138889</v>
+        <v>1.652072482638888</v>
       </c>
       <c r="D12" t="n">
-        <v>2.949246195254754</v>
+        <v>9.574495909895214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>sporulation__MP_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2338324652777778</v>
+        <v>0.007649739583333301</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9620225694444444</v>
+        <v>1.214789496527778</v>
       </c>
       <c r="D13" t="n">
-        <v>3.364772228142298</v>
+        <v>4.54939983558347</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>incubation__spl_end</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3591579861111112</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.024848090277776</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.25604495478288</v>
       </c>
     </row>
   </sheetData>
